--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Transformer Spec" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Transformer Spec'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Transformer Spec'!$A$1:$G$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -723,7 +726,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>NAUX   Auxiliary (ZCD)</t>
+          <t>NAUX   Auxiliary (VCC, ZCD)</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -733,12 +736,12 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>3 T</t>
+          <t>2 T</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>sense only</t>
+          <t>104 mA dc load (VCC)</t>
         </is>
       </c>
     </row>
@@ -954,28 +957,272 @@
     <row r="32" ht="14" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Core, bobbin, wire and winding arrangement are the supplier’s choice, provided section 3 is met.</t>
+          <t>Core, bobbin, wire and winding arrangement are the supplier’s choice, provided sections 3 and 5 are met.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>5.    SAFETY  INSULATION</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Household AV (TV) for the US, EU, Japan, Korea and China: IEC 62368-1 as adopted there, GB 4943.1-2022 in China (5000 m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Between</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Insulation grade</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>primary  |  secondary</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>REINFORCED</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Primary = NP1, NAUX and the CORE; secondary = NS2, NS3. Pollution degree 2, overvoltage category II, material group IIIb, 5000 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Creepage</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>primary  |  secondary</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>≥ 6.4 mm</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Everywhere: along the bobbin, over the flanges, at leads and pins (320 V rms row, reinforced = 2 × basic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Clearance</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>primary  |  secondary</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>≥ 4.5 mm</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>3.0 mm at 2000 m × 1.48 for 5000 m, rounded up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Separation</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>the two winding sections</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>≥ 6.4 mm</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>It is also the leakage (item 3-2): reach L.short WITHOUT narrowing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>NAUX wire</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>NAUX  |  secondary</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>TIW, reinforced</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Triple-insulated wire approved as reinforced insulation to IEC 62368-1, wound OVER the secondary; leads stay insulated up to the primary-row pins. Its approved frequency must cover the start-up frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Solid insulation</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>primary  |  secondary</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>DTI ≥ 0.4 mm  or  ≥ 2 tape layers</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Bobbin rated for reinforced insulation; each tape layer passes the reinforced test. Sleeve secondary leads that pass the core.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Electric strength</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>primary  |  secondary</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>3000 V ac 60 s  (4242 V dc)</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>NP1 + NAUX + core joined against NS2 + NS3 joined. Type test, no breakdown. Routine test voltage and time as agreed with the certifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>The working voltage behind item 2 is an estimate from the design (187 V rms, 373 V peak at 264 Vac); the certifying body measures it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="19">
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B18:F18"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>Primary = NP1, NAUX and the CORE; secondary = NS2, NS3. Pollution degree 2, overvoltage category II, material group IIIb, 5000 m.</t>
+          <t>Primary = NP1, NAUX; secondary = NS2, NS3 and the CORE. Pollution degree 2, overvoltage category II, material group IIIb, 5000 m.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Everywhere: along the bobbin, over the flanges, at leads and pins (320 V rms row, reinforced = 2 × basic).</t>
+          <t>Wherever the triple insulation ends: primary pins and stripped wire ends to the core and to secondary leads and pins (320 V rms row, reinforced = 2 × basic).</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="B40" s="9" t="inlineStr">
         <is>
           <t>4</t>
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Separation</t>
+          <t>NP1 wire</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>the two winding sections</t>
+          <t>NP1  |  secondary</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>≥ 6.4 mm</t>
+          <t>TIW-Litz, reinforced</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>It is also the leakage (item 3-2): reach L.short WITHOUT narrowing it.</t>
+          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin (split winding: part A, the crossing, part B). The gaps between the sections carry NO insulation: set them for item 3-2.</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Bobbin rated for reinforced insulation; each tape layer passes the reinforced test. Sleeve secondary leads that pass the core.</t>
+          <t>Where tape or sleeving carries it: each tape layer passes the reinforced test. Sleeve primary leads that leave the triple insulation near the core.</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>NP1 + NAUX + core joined against NS2 + NS3 joined. Type test, no breakdown. Routine test voltage and time as agreed with the certifier.</t>
+          <t>NP1 + NAUX joined against NS2 + NS3 + core joined. Type test, no breakdown. Routine test voltage and time as agreed with the certifier.</t>
         </is>
       </c>
     </row>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin (split winding: part A, the crossing, part B). The gaps between the sections carry NO insulation: set them for item 3-2.</t>
+          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin. The partition between the sections carries NO insulation; it sets item 3-2.</t>
         </is>
       </c>
     </row>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -588,7 +588,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   One transformer per set on TDK ETD 49/25/16DG (core B66367, coil former B66368, 20 pins).</t>
+          <t>•   One transformer per set on Magnetics E 60/22/16 (core 0R46016EC, custom two-section coil former, 20 pins).</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Centre tap is made on the PCB by joining pins 14, 15, 16 and 17 — do NOT join them inside the transformer.   Two pins per secondary terminal: confirm the pin current rating or bring the foil out as lugs.</t>
+          <t>Centre tap is made on the PCB by joining pins 14, 15, 16 and 17 — do NOT join them inside the transformer.   Two pins per secondary terminal, one per sub-winding: confirm the pin current rating.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Coil former TDK B66368 (ETD 49/25/16DG), 20 pins.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
+          <t>Coil former custom two-section for E 60/22/16, 20 pins, made to this specification.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Both measured at 1+2 – 4+5 of ONE transformer.   Item 2 is set by the winding arrangement (split primary or spacer): the vendor proposes it.</t>
+          <t>Both measured at 1+2 – 4+5 of ONE transformer.   Item 2 is set by the partition between the two sections of the former: trim it on the first samples.</t>
         </is>
       </c>
     </row>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -588,7 +588,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   One transformer per set on Magnetics E 60/22/16 (core 0R46016EC, custom two-section coil former, 20 pins).</t>
+          <t>•   One transformer per set on TDK E 60/22/16 (core PC47EE60-Z, custom coil former, 24 pins).</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>11+12 – 14+15</t>
+          <t>13+14+15 – 16+17+18</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>16+17 – 19+20</t>
+          <t>19+20+21 – 22+23+24</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>8 – 10</t>
+          <t>10 – 12</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -748,14 +748,14 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Centre tap is made on the PCB by joining pins 14, 15, 16 and 17 — do NOT join them inside the transformer.   Two pins per secondary terminal, one per sub-winding: confirm the pin current rating.</t>
+          <t>Centre tap is made on the PCB by joining pins 16, 17, 18, 19, 20 and 21 — do NOT join them inside the transformer.   Three pins per secondary terminal, one per Litz bundle: confirm the pin current rating.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Coil former custom two-section for E 60/22/16, 20 pins, made to this specification.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
+          <t>Custom coil former for E 60/22/16, 24 pins, made to this specification.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Both measured at 1+2 – 4+5 of ONE transformer.   Item 2 is set by the partition between the two sections of the former: trim it on the first samples.</t>
+          <t>Both measured at 1 – 3 of ONE transformer.   Item 2 is set by the window and the winding, the two sections touching: measure it, and each half alone, on the first samples.</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin. The partition between the sections carries NO insulation; it sets item 3-2.</t>
+          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin. Where the two sections touch, nothing else is between them.</t>
         </is>
       </c>
     </row>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -588,7 +588,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   One transformer per set on TDK E 60/22/16 (core PC47EE60-Z, custom coil former, 24 pins).</t>
+          <t>•   One transformer per set on TDK PQ 50/50 (core B65981A, B65982E coil former, 12 pins).</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>15 Ts</t>
+          <t>15 T</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>10.9 A   /   18.3 A</t>
+          <t>10.4 A   /   18.1 A</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>13+14+15 – 16+17+18</t>
+          <t>7 – 9</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>28.3 A   /   98.6 A</t>
+          <t>28.5 A   /   99.7 A</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>19+20+21 – 22+23+24</t>
+          <t>10 – 12</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>28.3 A   /   98.6 A</t>
+          <t>28.5 A   /   99.7 A</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>10 – 12</t>
+          <t>4 – 6</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -741,21 +741,21 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>104 mA dc load (VCC)</t>
+          <t>93 mA dc load (VCC)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Centre tap is made on the PCB by joining pins 16, 17, 18, 19, 20 and 21 — do NOT join them inside the transformer.   Three pins per secondary terminal, one per Litz bundle: confirm the pin current rating.</t>
+          <t>Centre tap is made on the PCB by joining pins 9 and 10 — do NOT join them inside the transformer.   One conductor per pin; a secondary pin carries its whole winding current: confirm the pin current rating, or bring the secondary ends straight out.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Custom coil former for E 60/22/16, 24 pins, made to this specification.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
+          <t>Coil former TDK B65982E (PQ 50/50), 12 pins, with a 3.0 mm partition added between the two sections.   Pin numbers as the data sheet gives them in its view from below, the pin side: pin 1 at the chamfered corner, 1 to 6 in one row and 7 to 12 in the other, 6 facing 7 and 1 facing 12. The data sheet prints 1, 6, 7 and 12; the pins between are counted. Seen from the component side of the board, left and right are exchanged.</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>31.00 µH    ±10 %</t>
+          <t>70.00 µH    ±10 %</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="B23" s="9" t="inlineStr">
         <is>
           <t>2</t>
@@ -849,12 +849,12 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>11.00 µH    ±10 %</t>
+          <t>25.00 µH    ±10 %</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>SECONDARY ALL SHORT (NS2 + NS3).   NAUX open.   Resonant inductor — a target, not a maximum.</t>
+          <t>EACH HALF: NS2 short alone, then NS3 short alone; the other half and NAUX open.   Both must pass.   Resonant inductor — a target, not a maximum.</t>
         </is>
       </c>
     </row>
@@ -881,21 +881,21 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Test current 16 A, normal temperature</t>
+          <t>Test current 14 A, normal temperature</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Both measured at 1 – 3 of ONE transformer.   Item 2 is set by the window and the winding, the two sections touching: measure it, and each half alone, on the first samples.</t>
+          <t>Both measured at 1 – 3 of ONE transformer.   Item 2 is set by the winding and the partition between the two sections: measure it, and each half alone, on the first samples; a thinner partition lowers it.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Item 2 follows the existing production part 26OP-LM83W clause 4-2, "SECONDARY ALL SHORT" — same vendor, same centre-tapped construction.   The auxiliary is NOT shorted.</t>
+          <t>Item 2, each half: in service only one half conducts at a time, and the two halves lie in different layers.   With NS2 and NS3 both shorted the reading is lower (about 23.1 µH estimated): record it, do not hold it to item 2.   The auxiliary is NOT shorted.</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>92  to  249 kHz</t>
+          <t>48  to  118 kHz</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Ae  ≥  103 mm²</t>
+          <t>Ae  ≥  208 mm²</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="32" ht="14" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Core, bobbin, wire and winding arrangement are the supplier’s choice, provided sections 3 and 5 are met.</t>
+          <t>The core, coil former and winding arrangement of the reference design set item 3-2. Another construction is acceptable only when sections 3 and 5 are met and the first samples are approved.</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin. Where the two sections touch, nothing else is between them.</t>
+          <t>Triple-insulated Litz approved as reinforced insulation to IEC 62368-1, one wire from pin to pin. The partition between the sections carries NO insulation; it sets item 3-2.</t>
         </is>
       </c>
     </row>

--- a/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>93 mA dc load (VCC)</t>
+          <t>144 mA dc load (VCC)</t>
         </is>
       </c>
     </row>
